--- a/results/log_pv_inst_fit/log_pv_inst_fit_densities_hdensity_estimates.xlsx
+++ b/results/log_pv_inst_fit/log_pv_inst_fit_densities_hdensity_estimates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,41 +462,11 @@
           <t>densities-ML_ErrorFE-queen-Running ML_ErrorFE:queen for log_pv_inst_fit ~ (densities): hdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>densities-PooledOLS-inverse_distance-Running PooledOLS:inverse_distance for log_pv_inst_fit ~ (densities): hdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>densities-PooledOLS-k_nearest-Running PooledOLS:k_nearest for log_pv_inst_fit ~ (densities): hdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>densities-PooledOLS-queen-Running PooledOLS:queen for log_pv_inst_fit ~ (densities): hdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>densities-PanelRE-inverse_distance-Running PanelRE:inverse_distance for log_pv_inst_fit ~ (densities): hdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>densities-PanelRE-k_nearest-Running PanelRE:k_nearest for log_pv_inst_fit ~ (densities): hdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>densities-PanelRE-queen-Running PanelRE:queen for log_pv_inst_fit ~ (densities): hdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>hdensity</t>
+          <t>D(Households)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,43 +512,13 @@
       <c r="J2" t="inlineStr">
         <is>
           <t>0.002***</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>-0.016***</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-0.016***</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>-0.016***</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>-0.007***</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>-0.007***</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>-0.007***</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>log_income</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -624,43 +564,13 @@
       <c r="J3" t="inlineStr">
         <is>
           <t>0.226**</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>-0.831***</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-0.831***</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>-0.831***</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>1.976***</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>1.976***</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>1.976***</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>log_hholds</t>
+          <t>Households</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -706,43 +616,13 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>0.002</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.041***</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0.041***</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0.041***</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0.003</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0.003</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0.003</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>log_sunny_hours</t>
+          <t>Sunny hours</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -788,126 +668,96 @@
       <c r="J5" t="inlineStr">
         <is>
           <t>0.185***</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.666***</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0.666***</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0.666***</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>-0.174***</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>-0.174***</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>-0.174***</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W_hdensity</t>
+          <t>Spatial term, ρ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.003</t>
+          <t>0.883***</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.008***</t>
+          <t>0.696***</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.005***</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>0.591***</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.964***</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.787***</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.693***</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W_log_income</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>0.545***</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0.777***</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.951***</t>
-        </is>
-      </c>
+          <t>Spatial term, λ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.973***</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.891***</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.841***</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W_log_hholds</t>
+          <t>W(D(Households))</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.062**</t>
+          <t>-0.003</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.006</t>
+          <t>-0.008***</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.006**</t>
+          <t>-0.005***</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -916,32 +766,26 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>W_log_sunny_hours</t>
+          <t>W(Income)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-0.284***</t>
+          <t>0.545***</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.338***</t>
+          <t>0.777***</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-0.325***</t>
+          <t>0.951***</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -950,891 +794,320 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>W_log_pv_inst_fit</t>
+          <t>W(Households)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.883***</t>
+          <t>-0.062**</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.696***</t>
+          <t>-0.006</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.591***</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.964***</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0.787***</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0.693***</t>
-        </is>
-      </c>
+          <t>-0.006**</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>r2</t>
+          <t>W(Sunny hours)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.851</t>
+          <t>-0.284***</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.829</t>
+          <t>-0.338***</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.812</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.849</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0.824</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0.804</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.006</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.260</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.367</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.263</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0.263</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0.263</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.035</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.035</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0.035</t>
-        </is>
-      </c>
+          <t>-0.325***</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>aic</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-9804.522</t>
+          <t>0.851</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-9395.438</t>
+          <t>0.829</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-9181.555</t>
+          <t>0.812</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-9773.295</t>
+          <t>0.849</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-9282.314</t>
+          <t>0.824</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-9013.699</t>
+          <t>0.804</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-9788.548</t>
+          <t>0.006</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-9197.775</t>
+          <t>0.260</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-8826.921</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>1102.669</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>1102.669</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>1102.669</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2525.973</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2525.973</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2525.973</t>
+          <t>0.367</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>schwarz</t>
+          <t>AIC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-9753.778</t>
+          <t>-9804.522</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-9344.694</t>
+          <t>-9395.438</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-9130.811</t>
+          <t>-9181.555</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-9745.104</t>
+          <t>-9773.295</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-9254.123</t>
+          <t>-9282.314</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-8985.508</t>
+          <t>-9013.699</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-9765.996</t>
+          <t>-9788.548</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-9175.223</t>
+          <t>-9197.775</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-8804.368</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>1130.860</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>1130.860</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>1130.860</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2554.164</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2554.164</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2554.164</t>
+          <t>-8826.921</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>llr</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4911.261</t>
+          <t>-9753.778</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4706.719</t>
+          <t>-9344.694</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4599.777</t>
+          <t>-9130.811</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4891.648</t>
+          <t>-9745.104</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>4646.157</t>
+          <t>-9254.123</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4511.849</t>
+          <t>-8985.508</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4898.274</t>
+          <t>-9765.996</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4602.888</t>
+          <t>-9175.223</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>4417.461</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>-546.335</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>-546.335</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>-546.335</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>-1257.987</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>-1257.987</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>-1257.987</t>
+          <t>-8804.368</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>n_obs</t>
+          <t>Log-Likelihood</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4911.261</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4706.719</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4599.777</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4891.648</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4646.157</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4511.849</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4898.274</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4602.888</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2076</t>
+          <t>4417.461</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tests</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df  p-value
-0       LM Marginal RE (LM1)    67.083558   1      0.0
-1  LM Marginal Spatial (LM2)    17.832644   1      0.0
-2             LM Joint (LMJ)  4818.206882   2      0.0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df  p-value
-0       LM Marginal RE (LM1)    67.083558   1      0.0
-1  LM Marginal Spatial (LM2)     8.454144   1      0.0
-2             LM Joint (LMJ)  4571.676244   2      0.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df       p-value
-0       LM Marginal RE (LM1)    67.083558   1  0.000000e+00
-1  LM Marginal Spatial (LM2)     7.656376   1  9.547918e-15
-2             LM Joint (LMJ)  4558.823775   2  0.000000e+00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test   Statistic df p-value
-0      LM Conditional Spatial  147.154889  1     0.0
-1  Hausman Specification Test  159.041712  4     0.0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test   Statistic df p-value
-0      LM Conditional Spatial   36.714303  1     0.0
-1  Hausman Specification Test  159.041712  4     0.0</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test   Statistic df p-value
-0      LM Conditional Spatial   24.414789  1     0.0
-1  Hausman Specification Test  159.041712  4     0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>outputs</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0           hdensity      0.00226  0.000655   3.448955  0.000563
-1         log_income    -0.069223  0.073355  -0.943676  0.345335
-2         log_hholds    -0.000066  0.001215  -0.054396   0.95662
-3    log_sunny_hours      0.16478  0.034422   4.787092  0.000002
-4         W_hdensity    -0.003274  0.007163  -0.457042  0.647641
-5       W_log_income     0.544922  0.136156   4.002179  0.000063
-6       W_log_hholds     -0.06245  0.022014  -2.836788  0.004557
-7  W_log_sunny_hours    -0.283969  0.054421  -5.218026       0.0
-8  W_log_pv_inst_fit     0.882622  0.029125  30.304241       0.0</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err   zt_stat      prob
-0           hdensity     0.001375  0.000697  1.972723  0.048527
-1         log_income     0.003436  0.075021  0.045802  0.963468
-2         log_hholds     0.000429  0.001299  0.329852  0.741512
-3    log_sunny_hours     0.147708  0.034955  4.225687  0.000024
-4         W_hdensity      -0.0082  0.001902 -4.310525  0.000016
-5       W_log_income     0.776514  0.093418  8.312237       0.0
-6       W_log_hholds    -0.005534  0.003881 -1.426011  0.153865
-7  W_log_sunny_hours    -0.338109  0.046078  -7.33771       0.0
-8  W_log_pv_inst_fit     0.695791  0.021369  32.56061       0.0</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0           hdensity      0.00102  0.000729   1.398965  0.161823
-1         log_income     0.039808  0.075128   0.529869  0.596203
-2         log_hholds     0.000586   0.00136   0.430797  0.666616
-3    log_sunny_hours     0.109954   0.03573   3.077343  0.002089
-4         W_hdensity    -0.004936   0.00123  -4.013229   0.00006
-5       W_log_income     0.951039  0.086335   11.01572       0.0
-6       W_log_hholds    -0.005914  0.002278  -2.595564  0.009444
-7  W_log_sunny_hours    -0.325023  0.044496  -7.304566       0.0
-8  W_log_pv_inst_fit     0.590533  0.021496  27.472042       0.0</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err     zt_stat      prob
-0           hdensity     0.002062  0.000652     3.16243  0.001565
-1         log_income      0.02042  0.025465    0.801884   0.42262
-2         log_hholds     0.000228  0.001218    0.186953  0.851698
-3    log_sunny_hours     0.070181  0.025263    2.777976   0.00547
-4  W_log_pv_inst_fit     0.963636  0.009311  103.497103       0.0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0           hdensity     0.001511  0.000705   2.142072  0.032188
-1         log_income     0.400663  0.037141  10.787661       0.0
-2         log_hholds     0.001024  0.001317   0.777423  0.436909
-3    log_sunny_hours     0.024023  0.025345   0.947832  0.343215
-4  W_log_pv_inst_fit     0.786666  0.015748  49.954656       0.0</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0           hdensity     0.001402  0.000744   1.884926   0.05944
-1         log_income     0.597355  0.041139   14.52045       0.0
-2         log_hholds     0.001169   0.00139   0.841187  0.400243
-3    log_sunny_hours      0.00332  0.026672   0.124461   0.90095
-4  W_log_pv_inst_fit     0.693367  0.017173  40.376428       0.0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         hdensity     0.002253  0.000656   3.433794  0.000595
-1       log_income    -0.051894  0.073115  -0.709768  0.477848
-2       log_hholds      0.00035  0.001209   0.289733  0.772021
-3  log_sunny_hours     0.164924  0.034466   4.785087  0.000002
-4           lambda     0.972774  0.007596  128.06018       0.0</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         hdensity     0.002348   0.00068   3.454757  0.000551
-1       log_income     0.143006  0.071954   1.987461  0.046871
-2       log_hholds      0.00131  0.001242   1.054332  0.291731
-3  log_sunny_hours     0.188939  0.035204   5.366914       0.0
-4           lambda     0.891492  0.010002  89.128714       0.0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         hdensity     0.002399  0.000684   3.507881  0.000452
-1       log_income     0.226257   0.07179   3.151654  0.001623
-2       log_hholds     0.001781  0.001237   1.439477  0.150015
-3  log_sunny_hours     0.185339  0.036436   5.086717       0.0
-4           lambda      0.84108  0.012293  68.421314       0.0</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     4.491356   0.49655   9.045131       0.0
-1         hdensity    -0.016334  0.000797 -20.493717       0.0
-2       log_income    -0.831384  0.074413 -11.172604       0.0
-3       log_hholds      0.04126  0.008537   4.832999  0.000001
-4  log_sunny_hours     0.665883  0.151287   4.401461  0.000011</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     4.491356   0.49655   9.045131       0.0
-1         hdensity    -0.016334  0.000797 -20.493717       0.0
-2       log_income    -0.831384  0.074413 -11.172604       0.0
-3       log_hholds      0.04126  0.008537   4.832999  0.000001
-4  log_sunny_hours     0.665883  0.151287   4.401461  0.000011</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     4.491356   0.49655   9.045131       0.0
-1         hdensity    -0.016334  0.000797 -20.493717       0.0
-2       log_income    -0.831384  0.074413 -11.172604       0.0
-3       log_hholds      0.04126  0.008537   4.832999  0.000001
-4  log_sunny_hours     0.665883  0.151287   4.401461  0.000011</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT    -4.735069  0.206569  -22.92251       0.0
-1         hdensity    -0.007234  0.001048  -6.899668       0.0
-2       log_income     1.976461  0.043457  45.480816       0.0
-3       log_hholds     0.003229  0.002283   1.414108   0.15733
-4  log_sunny_hours    -0.173959  0.043942  -3.958815  0.000075</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT    -4.735069  0.206569  -22.92251       0.0
-1         hdensity    -0.007234  0.001048  -6.899668       0.0
-2       log_income     1.976461  0.043457  45.480816       0.0
-3       log_hholds     0.003229  0.002283   1.414108   0.15733
-4  log_sunny_hours    -0.173959  0.043942  -3.958815  0.000075</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT    -4.735069  0.206569  -22.92251       0.0
-1         hdensity    -0.007234  0.001048  -6.899668       0.0
-2       log_income     1.976461  0.043457  45.480816       0.0
-3       log_hholds     0.003229  0.002283   1.414108   0.15733
-4  log_sunny_hours    -0.173959  0.043942  -3.958815  0.000075</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>effects</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_inverse_distance  \
-hdensity                                    -0.008635   
-log_income                                   4.052717   
-log_hholds                                  -0.532602   
-log_sunny_hours                             -1.015428   
-                 direct_ML_LagFE(SLX)_inverse_distance  \
-hdensity                                      0.002260   
-log_income                                   -0.069223   
-log_hholds                                   -0.000066   
-log_sunny_hours                               0.164780   
-                 indirect_ML_LagFE(SLX)_inverse_distance  
-hdensity                                       -0.010895  
-log_income                                      4.121940  
-log_hholds                                     -0.532536  
-log_sunny_hours                                -1.180208  </t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_k_nearest  \
-hdensity                             -0.022435   
-log_income                            2.563864   
-log_hholds                           -0.016781   
-log_sunny_hours                      -0.625892   
-                 direct_ML_LagFE(SLX)_k_nearest  \
-hdensity                               0.001375   
-log_income                             0.003436   
-log_hholds                             0.000429   
-log_sunny_hours                        0.147708   
-                 indirect_ML_LagFE(SLX)_k_nearest  
-hdensity                                -0.023810  
-log_income                               2.560428  
-log_hholds                              -0.017210  
-log_sunny_hours                         -0.773600  </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_queen  direct_ML_LagFE(SLX)_queen  \
-hdensity                         -0.009564                    0.001020   
-log_income                        2.419846                    0.039808   
-log_hholds                       -0.013011                    0.000586   
-log_sunny_hours                  -0.525242                    0.109954   
-                 indirect_ML_LagFE(SLX)_queen  
-hdensity                            -0.010584  
-log_income                           2.380038  
-log_hholds                          -0.013597  
-log_sunny_hours                     -0.635195  </t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_inverse_distance  \
-hdensity                                0.056702   
-log_income                              0.561536   
-log_hholds                              0.006260   
-log_sunny_hours                         1.929971   
-                 direct_ML_LagFE_inverse_distance  \
-hdensity                                 0.002062   
-log_income                               0.020420   
-log_hholds                               0.000228   
-log_sunny_hours                          0.070181   
-                 indirect_ML_LagFE_inverse_distance  
-hdensity                                   0.054641  
-log_income                                 0.541116  
-log_hholds                                 0.006033  
-log_sunny_hours                            1.859790  </t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_k_nearest  direct_ML_LagFE_k_nearest  \
-hdensity                         0.007080                   0.001511   
-log_income                       1.878100                   0.400663   
-log_hholds                       0.004800                   0.001024   
-log_sunny_hours                  0.112606                   0.024023   
-                 indirect_ML_LagFE_k_nearest  
-hdensity                            0.005570  
-log_income                          1.477437  
-log_hholds                          0.003776  
-log_sunny_hours                     0.088583  </t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_queen  direct_ML_LagFE_queen  \
-hdensity                     0.004573               0.001402   
-log_income                   1.948112               0.597355   
-log_hholds                   0.003812               0.001169   
-log_sunny_hours              0.010826               0.003320   
-                 indirect_ML_LagFE_queen  
-hdensity                        0.003171  
-log_income                      1.350757  
-log_hholds                      0.002643  
-log_sunny_hours                 0.007506  </t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>lambda</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>0.973***</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>0.891***</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>0.841***</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>CONSTANT</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>4.491***</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>4.491***</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>4.491***</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>-4.735***</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>-4.735***</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>-4.735***</t>
+          <t>N obs.</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2076</t>
         </is>
       </c>
     </row>
